--- a/.gitbook/assets/appx04.xlsx
+++ b/.gitbook/assets/appx04.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="109">
   <si>
     <t>類別</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -426,15 +426,35 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>最後更新日期：2026/05/14</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>處方集附錄四    R1 Side Chain與磺胺藥物</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>處方集附錄四    R1 Side Chain與磺胺藥物</t>
+    <t>處方集附錄四    β-lactam類抗生素及磺胺類藥物交叉過敏資料表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>處方集附錄四    β-lactam抗生素類及磺胺類藥物交叉過敏資料表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最後更新日期：2026/07/17</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>X</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -442,7 +462,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -519,6 +539,14 @@
       <family val="2"/>
       <charset val="136"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1106,6 +1134,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1118,6 +1152,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1165,18 +1205,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1566,69 +1594,73 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B5:Y24"/>
+  <dimension ref="A5:Y24"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.125" customWidth="1"/>
+    <col min="1" max="1" width="9.625" customWidth="1"/>
     <col min="2" max="2" width="20.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="24" width="3.625" customWidth="1"/>
+    <col min="3" max="14" width="3.625" customWidth="1"/>
+    <col min="15" max="15" width="9.5" customWidth="1"/>
+    <col min="16" max="24" width="3.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="2:25" ht="24" x14ac:dyDescent="0.25">
-      <c r="B5" s="71" t="s">
+    <row r="5" spans="1:25" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="56" t="s">
+        <v>101</v>
+      </c>
+      <c r="B5" s="56"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="56"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="56"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="56"/>
+      <c r="K5" s="56"/>
+      <c r="L5" s="56"/>
+      <c r="M5" s="56"/>
+      <c r="N5" s="56"/>
+      <c r="O5" s="56"/>
+    </row>
+    <row r="6" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="51"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="51"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="51"/>
+      <c r="K6" s="51"/>
+      <c r="L6" s="51"/>
+      <c r="M6" s="51"/>
+      <c r="N6" s="51"/>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="N7" s="50" t="s">
         <v>103</v>
       </c>
-      <c r="C5" s="71"/>
-      <c r="D5" s="71"/>
-      <c r="E5" s="71"/>
-      <c r="F5" s="71"/>
-      <c r="G5" s="71"/>
-      <c r="H5" s="71"/>
-      <c r="I5" s="71"/>
-      <c r="J5" s="71"/>
-      <c r="K5" s="71"/>
-      <c r="L5" s="71"/>
-      <c r="M5" s="71"/>
-      <c r="N5" s="71"/>
-    </row>
-    <row r="6" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="73"/>
-      <c r="C6" s="73"/>
-      <c r="D6" s="73"/>
-      <c r="E6" s="73"/>
-      <c r="F6" s="73"/>
-      <c r="G6" s="73"/>
-      <c r="H6" s="73"/>
-      <c r="I6" s="73"/>
-      <c r="J6" s="73"/>
-      <c r="K6" s="73"/>
-      <c r="L6" s="73"/>
-      <c r="M6" s="73"/>
-      <c r="N6" s="73"/>
-    </row>
-    <row r="7" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="N7" s="72" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="2:25" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="50" t="s">
+    </row>
+    <row r="8" spans="1:25" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="52" t="s">
         <v>99</v>
       </c>
-      <c r="C8" s="50"/>
-      <c r="D8" s="50"/>
-      <c r="E8" s="50"/>
-      <c r="F8" s="50"/>
-      <c r="G8" s="50"/>
-      <c r="H8" s="50"/>
-      <c r="I8" s="50"/>
-      <c r="J8" s="50"/>
-      <c r="K8" s="50"/>
-      <c r="L8" s="50"/>
-      <c r="M8" s="50"/>
-      <c r="N8" s="50"/>
-    </row>
-    <row r="9" spans="2:25" ht="111" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="52"/>
+      <c r="K8" s="52"/>
+      <c r="L8" s="52"/>
+      <c r="M8" s="52"/>
+      <c r="N8" s="52"/>
+    </row>
+    <row r="9" spans="1:25" ht="111" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="8"/>
       <c r="C9" s="9" t="s">
         <v>40</v>
@@ -1677,7 +1709,7 @@
       <c r="W9" s="12"/>
       <c r="X9" s="12"/>
     </row>
-    <row r="10" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B10" s="13" t="s">
         <v>40</v>
       </c>
@@ -1711,7 +1743,7 @@
       <c r="V10" s="1"/>
       <c r="W10" s="1"/>
     </row>
-    <row r="11" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B11" s="17" t="s">
         <v>41</v>
       </c>
@@ -1719,9 +1751,15 @@
         <v>55</v>
       </c>
       <c r="D11" s="19"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
+      <c r="E11" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>105</v>
+      </c>
       <c r="H11" s="20"/>
       <c r="I11" s="20"/>
       <c r="J11" s="20"/>
@@ -1739,17 +1777,23 @@
       <c r="V11" s="1"/>
       <c r="W11" s="1"/>
     </row>
-    <row r="12" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B12" s="17" t="s">
         <v>42</v>
       </c>
       <c r="C12" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="D12" s="20"/>
+      <c r="D12" s="20" t="s">
+        <v>104</v>
+      </c>
       <c r="E12" s="19"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
+      <c r="F12" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>106</v>
+      </c>
       <c r="H12" s="20"/>
       <c r="I12" s="20"/>
       <c r="J12" s="20"/>
@@ -1769,17 +1813,23 @@
       <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
     </row>
-    <row r="13" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B13" s="17" t="s">
         <v>43</v>
       </c>
       <c r="C13" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
+      <c r="D13" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>105</v>
+      </c>
       <c r="F13" s="19"/>
-      <c r="G13" s="20"/>
+      <c r="G13" s="20" t="s">
+        <v>107</v>
+      </c>
       <c r="H13" s="20"/>
       <c r="I13" s="20"/>
       <c r="J13" s="20"/>
@@ -1799,16 +1849,22 @@
       <c r="X13" s="1"/>
       <c r="Y13" s="1"/>
     </row>
-    <row r="14" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B14" s="17" t="s">
         <v>44</v>
       </c>
       <c r="C14" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
+      <c r="D14" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>105</v>
+      </c>
       <c r="G14" s="19"/>
       <c r="H14" s="20"/>
       <c r="I14" s="20"/>
@@ -1829,7 +1885,7 @@
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
     </row>
-    <row r="15" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B15" s="17" t="s">
         <v>56</v>
       </c>
@@ -1857,7 +1913,7 @@
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
     </row>
-    <row r="16" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B16" s="17" t="s">
         <v>57</v>
       </c>
@@ -1933,7 +1989,9 @@
       </c>
       <c r="K18" s="19"/>
       <c r="L18" s="20"/>
-      <c r="M18" s="20"/>
+      <c r="M18" s="20" t="s">
+        <v>106</v>
+      </c>
       <c r="N18" s="21"/>
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
@@ -1991,7 +2049,9 @@
       <c r="J20" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="K20" s="20"/>
+      <c r="K20" s="20" t="s">
+        <v>108</v>
+      </c>
       <c r="L20" s="20"/>
       <c r="M20" s="19"/>
       <c r="N20" s="21"/>
@@ -2038,21 +2098,21 @@
       <c r="Y21" s="1"/>
     </row>
     <row r="22" spans="2:25" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="51" t="s">
+      <c r="B22" s="53" t="s">
         <v>75</v>
       </c>
-      <c r="C22" s="52"/>
-      <c r="D22" s="52"/>
-      <c r="E22" s="52"/>
-      <c r="F22" s="52"/>
-      <c r="G22" s="52"/>
-      <c r="H22" s="52"/>
-      <c r="I22" s="52"/>
-      <c r="J22" s="52"/>
-      <c r="K22" s="52"/>
-      <c r="L22" s="52"/>
-      <c r="M22" s="52"/>
-      <c r="N22" s="53"/>
+      <c r="C22" s="54"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="54"/>
+      <c r="H22" s="54"/>
+      <c r="I22" s="54"/>
+      <c r="J22" s="54"/>
+      <c r="K22" s="54"/>
+      <c r="L22" s="54"/>
+      <c r="M22" s="54"/>
+      <c r="N22" s="55"/>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
       <c r="Q22" s="1"/>
@@ -2105,7 +2165,7 @@
   <mergeCells count="3">
     <mergeCell ref="B8:N8"/>
     <mergeCell ref="B22:N22"/>
-    <mergeCell ref="B5:N5"/>
+    <mergeCell ref="A5:O5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2140,26 +2200,26 @@
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="E4"/>
     </row>
-    <row r="5" spans="2:5" ht="27" x14ac:dyDescent="0.25">
-      <c r="B5" s="70" t="s">
+    <row r="5" spans="2:5" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="B5" s="57" t="s">
         <v>102</v>
       </c>
-      <c r="C5" s="70"/>
-      <c r="D5" s="70"/>
-      <c r="E5" s="70"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
     </row>
     <row r="6" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E6" s="72" t="s">
-        <v>101</v>
+      <c r="E6" s="50" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="2:5" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="62" t="s">
+      <c r="B7" s="66" t="s">
         <v>69</v>
       </c>
-      <c r="C7" s="63"/>
-      <c r="D7" s="63"/>
-      <c r="E7" s="64"/>
+      <c r="C7" s="67"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="68"/>
     </row>
     <row r="8" spans="2:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="48" t="s">
@@ -2176,7 +2236,7 @@
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="54" t="s">
+      <c r="B9" s="58" t="s">
         <v>63</v>
       </c>
       <c r="C9" s="31" t="s">
@@ -2190,7 +2250,7 @@
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="55"/>
+      <c r="B10" s="59"/>
       <c r="C10" s="29" t="s">
         <v>81</v>
       </c>
@@ -2202,7 +2262,7 @@
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="55"/>
+      <c r="B11" s="59"/>
       <c r="C11" s="29" t="s">
         <v>82</v>
       </c>
@@ -2214,7 +2274,7 @@
       </c>
     </row>
     <row r="12" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="56"/>
+      <c r="B12" s="60"/>
       <c r="C12" s="30" t="s">
         <v>83</v>
       </c>
@@ -2226,10 +2286,10 @@
       </c>
     </row>
     <row r="13" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="59" t="s">
+      <c r="B13" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="C13" s="65" t="s">
+      <c r="C13" s="69" t="s">
         <v>84</v>
       </c>
       <c r="D13" s="35" t="s">
@@ -2240,8 +2300,8 @@
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B14" s="60"/>
-      <c r="C14" s="66"/>
+      <c r="B14" s="64"/>
+      <c r="C14" s="70"/>
       <c r="D14" s="27" t="s">
         <v>5</v>
       </c>
@@ -2250,8 +2310,8 @@
       </c>
     </row>
     <row r="15" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="61"/>
-      <c r="C15" s="67"/>
+      <c r="B15" s="65"/>
+      <c r="C15" s="71"/>
       <c r="D15" s="38" t="s">
         <v>6</v>
       </c>
@@ -2260,10 +2320,10 @@
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B16" s="59" t="s">
+      <c r="B16" s="63" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="65" t="s">
+      <c r="C16" s="69" t="s">
         <v>85</v>
       </c>
       <c r="D16" s="35" t="s">
@@ -2274,8 +2334,8 @@
       </c>
     </row>
     <row r="17" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="60"/>
-      <c r="C17" s="66"/>
+      <c r="B17" s="64"/>
+      <c r="C17" s="70"/>
       <c r="D17" s="29" t="s">
         <v>65</v>
       </c>
@@ -2284,8 +2344,8 @@
       </c>
     </row>
     <row r="18" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="60"/>
-      <c r="C18" s="68"/>
+      <c r="B18" s="64"/>
+      <c r="C18" s="72"/>
       <c r="D18" s="28" t="s">
         <v>11</v>
       </c>
@@ -2294,7 +2354,7 @@
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B19" s="60"/>
+      <c r="B19" s="64"/>
       <c r="C19" s="29" t="s">
         <v>86</v>
       </c>
@@ -2306,7 +2366,7 @@
       </c>
     </row>
     <row r="20" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="61"/>
+      <c r="B20" s="65"/>
       <c r="C20" s="30" t="s">
         <v>13</v>
       </c>
@@ -2318,7 +2378,7 @@
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B21" s="59" t="s">
+      <c r="B21" s="63" t="s">
         <v>73</v>
       </c>
       <c r="C21" s="45" t="s">
@@ -2332,7 +2392,7 @@
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B22" s="60"/>
+      <c r="B22" s="64"/>
       <c r="C22" s="29" t="s">
         <v>88</v>
       </c>
@@ -2344,7 +2404,7 @@
       </c>
     </row>
     <row r="23" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="61"/>
+      <c r="B23" s="65"/>
       <c r="C23" s="47" t="s">
         <v>89</v>
       </c>
@@ -2356,7 +2416,7 @@
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B24" s="59" t="s">
+      <c r="B24" s="63" t="s">
         <v>17</v>
       </c>
       <c r="C24" s="45" t="s">
@@ -2370,8 +2430,8 @@
       </c>
     </row>
     <row r="25" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="60"/>
-      <c r="C25" s="69" t="s">
+      <c r="B25" s="64"/>
+      <c r="C25" s="73" t="s">
         <v>90</v>
       </c>
       <c r="D25" s="32" t="s">
@@ -2382,8 +2442,8 @@
       </c>
     </row>
     <row r="26" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="60"/>
-      <c r="C26" s="66"/>
+      <c r="B26" s="64"/>
+      <c r="C26" s="70"/>
       <c r="D26" s="29" t="s">
         <v>21</v>
       </c>
@@ -2392,8 +2452,8 @@
       </c>
     </row>
     <row r="27" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="60"/>
-      <c r="C27" s="68"/>
+      <c r="B27" s="64"/>
+      <c r="C27" s="72"/>
       <c r="D27" s="28" t="s">
         <v>22</v>
       </c>
@@ -2402,7 +2462,7 @@
       </c>
     </row>
     <row r="28" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="60"/>
+      <c r="B28" s="64"/>
       <c r="C28" s="47" t="s">
         <v>91</v>
       </c>
@@ -2414,7 +2474,7 @@
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B29" s="54" t="s">
+      <c r="B29" s="58" t="s">
         <v>25</v>
       </c>
       <c r="C29" s="45" t="s">
@@ -2428,7 +2488,7 @@
       </c>
     </row>
     <row r="30" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="56"/>
+      <c r="B30" s="60"/>
       <c r="C30" s="47" t="s">
         <v>92</v>
       </c>
@@ -2454,7 +2514,7 @@
       </c>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B32" s="54" t="s">
+      <c r="B32" s="58" t="s">
         <v>31</v>
       </c>
       <c r="C32" s="31" t="s">
@@ -2468,8 +2528,8 @@
       </c>
     </row>
     <row r="33" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="55"/>
-      <c r="C33" s="57" t="s">
+      <c r="B33" s="59"/>
+      <c r="C33" s="61" t="s">
         <v>94</v>
       </c>
       <c r="D33" s="29" t="s">
@@ -2480,8 +2540,8 @@
       </c>
     </row>
     <row r="34" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="55"/>
-      <c r="C34" s="58"/>
+      <c r="B34" s="59"/>
+      <c r="C34" s="62"/>
       <c r="D34" s="28" t="s">
         <v>32</v>
       </c>
@@ -2490,7 +2550,7 @@
       </c>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B35" s="55"/>
+      <c r="B35" s="59"/>
       <c r="C35" s="37" t="s">
         <v>95</v>
       </c>
@@ -2502,7 +2562,7 @@
       </c>
     </row>
     <row r="36" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="56"/>
+      <c r="B36" s="60"/>
       <c r="C36" s="47" t="s">
         <v>96</v>
       </c>
